--- a/astro-site/public/dl/catering-checklist-templates/BONUS-02-catering-events-calendar.xlsx
+++ b/astro-site/public/dl/catering-checklist-templates/BONUS-02-catering-events-calendar.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Early Feb — Super Bowl Sunday (2nd Sunday)</t>
+          <t>Feb — Super Bowl Sunday (2nd Sunday)</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -781,22 +781,22 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>April — First Communion season (starts)</t>
+          <t>Mar 17 — St. Patrick's Day</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Celebration</t>
+          <t>Holiday</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Kids' + adult menus, themed decor</t>
+          <t>Corporate parties and family gatherings with a themed menu; alcohol only under the license your state requires (yours or the venue's), 21+ with ID</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>2–3 months</t>
+          <t>3 weeks</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Mar 17 — St. Patrick's Day</t>
+          <t>Mar–Apr — Easter &amp; Passover (dates vary)</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Corporate parties and family gatherings with a themed menu; alcohol only under your license or with licensed bartenders (21+ with ID)</t>
+          <t>Easter brunch and family dinners (ham, lamb, seasonal desserts); Passover seder if your clients ask (kosher only with a certified kitchen and supervision)</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -833,22 +833,22 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Mar–Apr — Easter &amp; Passover (dates vary)</t>
+          <t>April — First Communions (season starts), quinceaneras &amp; bar/bat mitzvahs</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>Celebration</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Easter brunch and family dinners (ham, lamb, seasonal desserts); Passover seder if your clients ask (kosher only with a certified kitchen and supervision)</t>
+          <t>Kids' + adult menus, themed decor</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>3 weeks</t>
+          <t>2–3 months</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -885,7 +885,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>May — First Communions (peak) &amp; Mother's Day (2nd Sunday)</t>
+          <t>May — First Communions &amp; quinceaneras (peak) + Mother's Day (2nd Sunday)</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Outdoor events, rain plan Bs, tents</t>
+          <t>Graduation open houses and party trays, outdoor events, rain plan Bs, tents</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Holiday menus: prime rib, ham, seafood, seasonal desserts</t>
+          <t>Holiday menus: prime rib, ham, seafood, seasonal desserts; for Hanukkah (dates vary), latkes and brisket</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
